--- a/automation/reports/Load_Test_Report.xlsx
+++ b/automation/reports/Load_Test_Report.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-30T10:36:14Z</t>
+          <t>2026-07-30T11:44:27Z</t>
         </is>
       </c>
     </row>
